--- a/docs/EP-13257_externe_poziadavky_rozdiely.xlsx
+++ b/docs/EP-13257_externe_poziadavky_rozdiely.xlsx
@@ -7,10 +7,10 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chybajuce na trnavavuc-test" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chýbajúce na trnavavuc-test" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Chybajuce na trnavavuc-test'!$A$4:$H$57</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Chýbajúce na trnavavuc-test'!$A$4:$H$51</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -500,30 +500,30 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H59"/>
+  <dimension ref="A1:H53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
     <col width="13" customWidth="1" min="2" max="2"/>
-    <col width="62" customWidth="1" min="3" max="3"/>
-    <col width="34" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="64" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
     <col width="11" customWidth="1" min="7" max="7"/>
-    <col width="42" customWidth="1" min="8" max="8"/>
+    <col width="46" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>EP-13257 - Externe poziadavky (CPS/OvZP): nasadene na poseidon-test, chybaju na trnavavuc_test</t>
+          <t>EP-13257 – Externé požiadavky (CPS/OvZP): nasadené na poseidon-test, chýbajú na trnavavuc_test</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Porovnanie vetiev origin/poseidon-test vs origin/trnavavuc_test (client + server), stav k 16.7.2026. Zdroj verzii: pole Fix Version v Jire.</t>
+          <t>Porovnanie vetiev origin/poseidon-test vs origin/trnavavuc_test (client + server), stav k 16.7.2026. Zoznam na úrovni story/bug – sub-tasky sú zastúpené nadradenou story. Zdroj verzií: pole Fix Version v Jire.</t>
         </is>
       </c>
     </row>
@@ -540,7 +540,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Nazov</t>
+          <t>Názov</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -555,7 +555,7 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>Datum releasu</t>
+          <t>Dátum releasu</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
@@ -565,7 +565,7 @@
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t>Poznamka</t>
+          <t>Poznámka</t>
         </is>
       </c>
     </row>
@@ -587,7 +587,7 @@
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>EP-11645 - PSK_Externe poziadavky</t>
+          <t>EP-11645 – PSK_Externé požiadavky</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -625,7 +625,7 @@
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>EP-11645 - PSK_Externe poziadavky</t>
+          <t>EP-11645 – PSK_Externé požiadavky</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -663,7 +663,7 @@
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>EP-11645 - PSK_Externe poziadavky</t>
+          <t>EP-11645 – PSK_Externé požiadavky</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -701,7 +701,7 @@
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>EP-11645 - PSK_Externe poziadavky</t>
+          <t>EP-11645 – PSK_Externé požiadavky</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -739,7 +739,7 @@
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>EP-11645 - PSK_Externe poziadavky</t>
+          <t>EP-11645 – PSK_Externé požiadavky</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -777,7 +777,7 @@
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>EP-11645 - PSK_Externe poziadavky</t>
+          <t>EP-11645 – PSK_Externé požiadavky</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -815,7 +815,7 @@
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>EP-11645 - PSK_Externe poziadavky</t>
+          <t>EP-11645 – PSK_Externé požiadavky</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -853,7 +853,7 @@
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>EP-11645 - PSK_Externe poziadavky</t>
+          <t>EP-11645 – PSK_Externé požiadavky</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -891,7 +891,7 @@
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>EP-11645 - PSK_Externe poziadavky</t>
+          <t>EP-11645 – PSK_Externé požiadavky</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -929,7 +929,7 @@
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>EP-11645 - PSK_Externe poziadavky</t>
+          <t>EP-11645 – PSK_Externé požiadavky</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -967,7 +967,7 @@
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>EP-11645 - PSK_Externe poziadavky</t>
+          <t>EP-11645 – PSK_Externé požiadavky</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -1005,7 +1005,7 @@
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>EP-11645 - PSK_Externe poziadavky</t>
+          <t>EP-11645 – PSK_Externé požiadavky</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -1043,7 +1043,7 @@
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>EP-11645 - PSK_Externe poziadavky</t>
+          <t>EP-11645 – PSK_Externé požiadavky</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -1066,32 +1066,32 @@
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
         <is>
-          <t>EP-11724</t>
+          <t>EP-11736</t>
         </is>
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>Dev Sub-task</t>
+          <t>Story</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>PSK - Externé požiadavky – upravovanie atributov len pre zodpovedné osoby a schalovatelov_DEVELOPMENT</t>
+          <t>PSK - Externé požiadavky – skrytie protokolu v module externé požiadavky</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr">
         <is>
-          <t>EP-11645 - PSK_Externe poziadavky</t>
+          <t>EP-11645 – PSK_Externé požiadavky</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
         <is>
-          <t>psk-2.7.0, psk-2.7.2</t>
+          <t>psk-2.7.0</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>2025-12-18, 2026-01-13</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="G18" s="5" t="inlineStr">
@@ -1099,31 +1099,27 @@
           <t>DONE</t>
         </is>
       </c>
-      <c r="H18" s="6" t="inlineStr">
-        <is>
-          <t>prevzate z nadradenej story EP-11723</t>
-        </is>
-      </c>
+      <c r="H18" s="6" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>EP-11756</t>
+          <t>EP-11757</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>Bug Sub-task</t>
+          <t>Story</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>PSK - Externé požiadavky - upravovanie atribútov v schvaľovacom procese</t>
+          <t>PSK - Externé požiadavky – potvrzdovacie okno v schvaľovacom procese</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>EP-11645 - PSK_Externe poziadavky</t>
+          <t>EP-11645 – PSK_Externé požiadavky</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -1146,22 +1142,22 @@
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>EP-11757</t>
+          <t>EP-11763</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>Story</t>
+          <t>Chyba</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>PSK - Externé požiadavky – potvrzdovacie okno v schvaľovacom procese</t>
+          <t>PSK-TEST - CPS poziadavky - Nie je mozne ulozit, odoslat  poziadavku</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
         <is>
-          <t>EP-11645 - PSK_Externe poziadavky</t>
+          <t>EP-11645 – PSK_Externé požiadavky</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -1184,7 +1180,7 @@
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>EP-11763</t>
+          <t>EP-11821</t>
         </is>
       </c>
       <c r="B21" s="5" t="inlineStr">
@@ -1194,22 +1190,22 @@
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>PSK-TEST - CPS poziadavky - Nie je mozne ulozit, odoslat  poziadavku</t>
+          <t>PSK-TEST - Externé požiadavky - Nespravny počet schvaľovateľov ak je odoslaná vrátená požiadavka</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>EP-11645 - PSK_Externe poziadavky</t>
+          <t>EP-11645 – PSK_Externé požiadavky</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
         <is>
-          <t>psk-2.7.0</t>
+          <t>psk-2.9.0</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>neuvolnena</t>
         </is>
       </c>
       <c r="G21" s="5" t="inlineStr">
@@ -1217,37 +1213,41 @@
           <t>DONE</t>
         </is>
       </c>
-      <c r="H21" s="6" t="inlineStr"/>
+      <c r="H21" s="6" t="inlineStr">
+        <is>
+          <t>verzia zatiaľ nie je označená ako released</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
         <is>
-          <t>EP-11821</t>
+          <t>EP-13049</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>Chyba</t>
+          <t>Story</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>PSK-TEST - Externé požiadavky - Nespravny počet schvaľovateľov ak je odoslaná vrátená požiadavka</t>
+          <t>PSK - Externé požiadavky – pozorovatel / zodpovedna osoba - skrytie nastavenie podla druhu</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>EP-11645 - PSK_Externe poziadavky</t>
+          <t>EP-11645 – PSK_Externé požiadavky</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
         <is>
-          <t>psk-2.9.0</t>
+          <t>psk-2.7.0</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>neuvolnena</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="G22" s="5" t="inlineStr">
@@ -1255,41 +1255,37 @@
           <t>DONE</t>
         </is>
       </c>
-      <c r="H22" s="6" t="inlineStr">
-        <is>
-          <t>verzia psk-2.9.0 este nie je oznacena ako released</t>
-        </is>
-      </c>
+      <c r="H22" s="6" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="7" t="inlineStr">
         <is>
-          <t>EP-11737</t>
+          <t>EP-11784</t>
         </is>
       </c>
       <c r="B23" s="8" t="inlineStr">
         <is>
-          <t>Dev Sub-task</t>
+          <t>Story</t>
         </is>
       </c>
       <c r="C23" s="9" t="inlineStr">
         <is>
-          <t>PSK - Externé požiadavky –  skrytie protokolu v module externé požiadavky_DEVELOPMENT</t>
+          <t>Základná finančná kontrola - požiadavky CPS - premenovanie ZFK na FK</t>
         </is>
       </c>
       <c r="D23" s="9" t="inlineStr">
         <is>
-          <t>EP-11736 - skrytie protokolu</t>
+          <t>EP-11785 – Základná finančná kontrola (novela)</t>
         </is>
       </c>
       <c r="E23" s="8" t="inlineStr">
         <is>
-          <t>psk-2.7.0</t>
+          <t>psk-2.7.1</t>
         </is>
       </c>
       <c r="F23" s="8" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="G23" s="8" t="inlineStr">
@@ -1297,41 +1293,37 @@
           <t>DONE</t>
         </is>
       </c>
-      <c r="H23" s="9" t="inlineStr">
-        <is>
-          <t>prevzate z nadradenej story EP-11736</t>
-        </is>
-      </c>
+      <c r="H23" s="9" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="7" t="inlineStr">
         <is>
-          <t>EP-11752</t>
+          <t>EP-11786</t>
         </is>
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>Bug Sub-task</t>
+          <t>Story</t>
         </is>
       </c>
       <c r="C24" s="9" t="inlineStr">
         <is>
-          <t>PSK - Externé požiadavky - skrytie protokolu</t>
+          <t>Základná finančná kontrola - požiadavky CPS - úprava procesu ZFK</t>
         </is>
       </c>
       <c r="D24" s="9" t="inlineStr">
         <is>
-          <t>EP-11736 - skrytie protokolu</t>
+          <t>EP-11785 – Základná finančná kontrola (novela)</t>
         </is>
       </c>
       <c r="E24" s="8" t="inlineStr">
         <is>
-          <t>psk-2.7.0</t>
+          <t>psk-2.7.1</t>
         </is>
       </c>
       <c r="F24" s="8" t="inlineStr">
         <is>
-          <t>2025-12-18</t>
+          <t>2026-01-01</t>
         </is>
       </c>
       <c r="G24" s="8" t="inlineStr">
@@ -1342,47 +1334,47 @@
       <c r="H24" s="9" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="4" t="inlineStr">
-        <is>
-          <t>EP-11786</t>
-        </is>
-      </c>
-      <c r="B25" s="5" t="inlineStr">
-        <is>
-          <t>Story</t>
-        </is>
-      </c>
-      <c r="C25" s="6" t="inlineStr">
-        <is>
-          <t>Základná finančná kontrola - požiadavky CPS - úprava procesu ZFK</t>
-        </is>
-      </c>
-      <c r="D25" s="6" t="inlineStr">
-        <is>
-          <t>EP-11785 - ZFK novela</t>
-        </is>
-      </c>
-      <c r="E25" s="5" t="inlineStr">
-        <is>
-          <t>psk-2.7.1</t>
-        </is>
-      </c>
-      <c r="F25" s="5" t="inlineStr">
-        <is>
-          <t>2026-01-01</t>
-        </is>
-      </c>
-      <c r="G25" s="5" t="inlineStr">
-        <is>
-          <t>DONE</t>
-        </is>
-      </c>
-      <c r="H25" s="6" t="inlineStr"/>
+      <c r="A25" s="7" t="inlineStr">
+        <is>
+          <t>EP-11787</t>
+        </is>
+      </c>
+      <c r="B25" s="8" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="C25" s="9" t="inlineStr">
+        <is>
+          <t>Základná finančná kontrola - požiadavky CPS - protokol</t>
+        </is>
+      </c>
+      <c r="D25" s="9" t="inlineStr">
+        <is>
+          <t>EP-11785 – Základná finančná kontrola (novela)</t>
+        </is>
+      </c>
+      <c r="E25" s="8" t="inlineStr">
+        <is>
+          <t>psk-2.7.0, psk-2.7.1</t>
+        </is>
+      </c>
+      <c r="F25" s="8" t="inlineStr">
+        <is>
+          <t>2025-12-18, 2026-01-01</t>
+        </is>
+      </c>
+      <c r="G25" s="8" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="H25" s="9" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>EP-11787</t>
+          <t>EP-12640</t>
         </is>
       </c>
       <c r="B26" s="5" t="inlineStr">
@@ -1392,22 +1384,22 @@
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>Základná finančná kontrola - požiadavky CPS - protokol</t>
+          <t>Požiadavky CPS - Druhy požiadavky - samostatný číselnik v nastaveniach systému</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>EP-11785 - ZFK novela</t>
+          <t>EP-12353 – EES zmenové požiadavky</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
         <is>
-          <t>psk-2.7.0, psk-2.7.1</t>
+          <t>poseidon-2.10.0</t>
         </is>
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>2025-12-18, 2026-01-01</t>
+          <t>2026-05-05</t>
         </is>
       </c>
       <c r="G26" s="5" t="inlineStr">
@@ -1418,718 +1410,718 @@
       <c r="H26" s="6" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="7" t="inlineStr">
-        <is>
-          <t>EP-12640</t>
-        </is>
-      </c>
-      <c r="B27" s="8" t="inlineStr">
-        <is>
-          <t>Story</t>
-        </is>
-      </c>
-      <c r="C27" s="9" t="inlineStr">
-        <is>
-          <t>Požiadavky CPS - Druhy požiadavky - samostatný číselnik v nastaveniach systému</t>
-        </is>
-      </c>
-      <c r="D27" s="9" t="inlineStr">
-        <is>
-          <t>EP-12353 - EES zmenove poziadavky</t>
-        </is>
-      </c>
-      <c r="E27" s="8" t="inlineStr">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>EP-12652</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>Požiadavky CPS - Radanie prístupov- zodpovedná osoba/pozorovatel - Podľa druhu požiadavky a Ovzp</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t>EP-12353 – EES zmenové požiadavky</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="inlineStr">
         <is>
           <t>poseidon-2.10.0</t>
         </is>
       </c>
-      <c r="F27" s="8" t="inlineStr">
+      <c r="F27" s="5" t="inlineStr">
         <is>
           <t>2026-05-05</t>
         </is>
       </c>
-      <c r="G27" s="8" t="inlineStr">
-        <is>
-          <t>DONE</t>
-        </is>
-      </c>
-      <c r="H27" s="9" t="inlineStr"/>
+      <c r="G27" s="5" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="H27" s="6" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="7" t="inlineStr">
-        <is>
-          <t>EP-12806</t>
-        </is>
-      </c>
-      <c r="B28" s="8" t="inlineStr">
-        <is>
-          <t>Bug Sub-task</t>
-        </is>
-      </c>
-      <c r="C28" s="9" t="inlineStr">
-        <is>
-          <t>Požiadavky CPS - Druhy požiadavky - V prehlade poziadaviek sa nezobrazuju hodnoty v stlpci Druh poziadavky</t>
-        </is>
-      </c>
-      <c r="D28" s="9" t="inlineStr">
-        <is>
-          <t>EP-12353 - EES zmenove poziadavky</t>
-        </is>
-      </c>
-      <c r="E28" s="8" t="inlineStr">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>EP-12667</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>Požiadavky CPS - Nový stav požiadavky - Podmienečne súhlasím</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="inlineStr">
+        <is>
+          <t>EP-12353 – EES zmenové požiadavky</t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="inlineStr">
         <is>
           <t>poseidon-2.10.0</t>
         </is>
       </c>
-      <c r="F28" s="8" t="inlineStr">
+      <c r="F28" s="5" t="inlineStr">
         <is>
           <t>2026-05-05</t>
         </is>
       </c>
-      <c r="G28" s="8" t="inlineStr">
-        <is>
-          <t>DONE</t>
-        </is>
-      </c>
-      <c r="H28" s="9" t="inlineStr"/>
+      <c r="G28" s="5" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="H28" s="6" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="7" t="inlineStr">
-        <is>
-          <t>EP-12652</t>
-        </is>
-      </c>
-      <c r="B29" s="8" t="inlineStr">
-        <is>
-          <t>Story</t>
-        </is>
-      </c>
-      <c r="C29" s="9" t="inlineStr">
-        <is>
-          <t>Požiadavky CPS - Radanie prístupov- zodpovedná osoba/pozorovatel - Podľa druhu požiadavky a Ovzp</t>
-        </is>
-      </c>
-      <c r="D29" s="9" t="inlineStr">
-        <is>
-          <t>EP-12353 - EES zmenove poziadavky</t>
-        </is>
-      </c>
-      <c r="E29" s="8" t="inlineStr">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>EP-12670</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>Požiadavky CPS - vytiahnutie názvu pozície do nastavení systému + zobrazenie pri procese</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="inlineStr">
+        <is>
+          <t>EP-12353 – EES zmenové požiadavky</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="inlineStr">
         <is>
           <t>poseidon-2.10.0</t>
         </is>
       </c>
-      <c r="F29" s="8" t="inlineStr">
+      <c r="F29" s="5" t="inlineStr">
         <is>
           <t>2026-05-05</t>
         </is>
       </c>
-      <c r="G29" s="8" t="inlineStr">
-        <is>
-          <t>DONE</t>
-        </is>
-      </c>
-      <c r="H29" s="9" t="inlineStr"/>
+      <c r="G29" s="5" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="H29" s="6" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="7" t="inlineStr">
-        <is>
-          <t>EP-12667</t>
-        </is>
-      </c>
-      <c r="B30" s="8" t="inlineStr">
-        <is>
-          <t>Story</t>
-        </is>
-      </c>
-      <c r="C30" s="9" t="inlineStr">
-        <is>
-          <t>Požiadavky CPS - Nový stav požiadavky - Podmienečne súhlasím</t>
-        </is>
-      </c>
-      <c r="D30" s="9" t="inlineStr">
-        <is>
-          <t>EP-12353 - EES zmenove poziadavky</t>
-        </is>
-      </c>
-      <c r="E30" s="8" t="inlineStr">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>EP-12673</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="C30" s="6" t="inlineStr">
+        <is>
+          <t>Požiadavky - povinný komentár pri zamietnutí / Podmienečnom súhlase - požiadavka ZFK</t>
+        </is>
+      </c>
+      <c r="D30" s="6" t="inlineStr">
+        <is>
+          <t>EP-12353 – EES zmenové požiadavky</t>
+        </is>
+      </c>
+      <c r="E30" s="5" t="inlineStr">
         <is>
           <t>poseidon-2.10.0</t>
         </is>
       </c>
-      <c r="F30" s="8" t="inlineStr">
+      <c r="F30" s="5" t="inlineStr">
         <is>
           <t>2026-05-05</t>
         </is>
       </c>
-      <c r="G30" s="8" t="inlineStr">
-        <is>
-          <t>DONE</t>
-        </is>
-      </c>
-      <c r="H30" s="9" t="inlineStr"/>
+      <c r="G30" s="5" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="H30" s="6" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="7" t="inlineStr">
-        <is>
-          <t>EP-12816</t>
-        </is>
-      </c>
-      <c r="B31" s="8" t="inlineStr">
-        <is>
-          <t>Bug Sub-task</t>
-        </is>
-      </c>
-      <c r="C31" s="9" t="inlineStr">
-        <is>
-          <t>Požiadavky CPS - Nový stav požiadavky - Ak je poziadavka podmienecne schvalena, stav poziadavky sa nezmenil</t>
-        </is>
-      </c>
-      <c r="D31" s="9" t="inlineStr">
-        <is>
-          <t>EP-12353 - EES zmenove poziadavky</t>
-        </is>
-      </c>
-      <c r="E31" s="8" t="inlineStr">
+      <c r="A31" s="4" t="inlineStr">
+        <is>
+          <t>EP-12774</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="C31" s="6" t="inlineStr">
+        <is>
+          <t>Požiadavky - doplnenie informácie o súvisiacej požiadavke</t>
+        </is>
+      </c>
+      <c r="D31" s="6" t="inlineStr">
+        <is>
+          <t>EP-12353 – EES zmenové požiadavky</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="inlineStr">
         <is>
           <t>poseidon-2.10.0</t>
         </is>
       </c>
-      <c r="F31" s="8" t="inlineStr">
+      <c r="F31" s="5" t="inlineStr">
         <is>
           <t>2026-05-05</t>
         </is>
       </c>
-      <c r="G31" s="8" t="inlineStr">
-        <is>
-          <t>DONE</t>
-        </is>
-      </c>
-      <c r="H31" s="9" t="inlineStr"/>
+      <c r="G31" s="5" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="H31" s="6" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="7" t="inlineStr">
-        <is>
-          <t>EP-12670</t>
-        </is>
-      </c>
-      <c r="B32" s="8" t="inlineStr">
-        <is>
-          <t>Story</t>
-        </is>
-      </c>
-      <c r="C32" s="9" t="inlineStr">
-        <is>
-          <t>Požiadavky CPS - vytiahnutie názvu pozície do nastavení systému + zobrazenie pri procese</t>
-        </is>
-      </c>
-      <c r="D32" s="9" t="inlineStr">
-        <is>
-          <t>EP-12353 - EES zmenove poziadavky</t>
-        </is>
-      </c>
-      <c r="E32" s="8" t="inlineStr">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>EP-12792</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="C32" s="6" t="inlineStr">
+        <is>
+          <t>Externé požiadavky - Nový atribút - Termín spracovania</t>
+        </is>
+      </c>
+      <c r="D32" s="6" t="inlineStr">
+        <is>
+          <t>EP-12353 – EES zmenové požiadavky</t>
+        </is>
+      </c>
+      <c r="E32" s="5" t="inlineStr">
         <is>
           <t>poseidon-2.10.0</t>
         </is>
       </c>
-      <c r="F32" s="8" t="inlineStr">
+      <c r="F32" s="5" t="inlineStr">
         <is>
           <t>2026-05-05</t>
         </is>
       </c>
-      <c r="G32" s="8" t="inlineStr">
-        <is>
-          <t>DONE</t>
-        </is>
-      </c>
-      <c r="H32" s="9" t="inlineStr"/>
+      <c r="G32" s="5" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="H32" s="6" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="7" t="inlineStr">
-        <is>
-          <t>EP-12673</t>
-        </is>
-      </c>
-      <c r="B33" s="8" t="inlineStr">
-        <is>
-          <t>Story</t>
-        </is>
-      </c>
-      <c r="C33" s="9" t="inlineStr">
-        <is>
-          <t>Požiadavky - povinný komentár pri zamietnutí / Podmienečnom súhlase - požiadavka ZFK</t>
-        </is>
-      </c>
-      <c r="D33" s="9" t="inlineStr">
-        <is>
-          <t>EP-12353 - EES zmenove poziadavky</t>
-        </is>
-      </c>
-      <c r="E33" s="8" t="inlineStr">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>EP-12807</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>Chyba</t>
+        </is>
+      </c>
+      <c r="C33" s="6" t="inlineStr">
+        <is>
+          <t>Požiadavky CPS - Po kliknuti na tlacidlo Ulozit je pouzivatel odhlaseny zo systemu, ak je stav poziadavky Odoslana na OvZP</t>
+        </is>
+      </c>
+      <c r="D33" s="6" t="inlineStr">
+        <is>
+          <t>EP-12353 – EES zmenové požiadavky</t>
+        </is>
+      </c>
+      <c r="E33" s="5" t="inlineStr">
         <is>
           <t>poseidon-2.10.0</t>
         </is>
       </c>
-      <c r="F33" s="8" t="inlineStr">
+      <c r="F33" s="5" t="inlineStr">
         <is>
           <t>2026-05-05</t>
         </is>
       </c>
-      <c r="G33" s="8" t="inlineStr">
-        <is>
-          <t>DONE</t>
-        </is>
-      </c>
-      <c r="H33" s="9" t="inlineStr"/>
+      <c r="G33" s="5" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="H33" s="6" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="7" t="inlineStr">
-        <is>
-          <t>EP-12774</t>
-        </is>
-      </c>
-      <c r="B34" s="8" t="inlineStr">
-        <is>
-          <t>Story</t>
-        </is>
-      </c>
-      <c r="C34" s="9" t="inlineStr">
-        <is>
-          <t>Požiadavky - doplnenie informácie o súvisiacej požiadavke</t>
-        </is>
-      </c>
-      <c r="D34" s="9" t="inlineStr">
-        <is>
-          <t>EP-12353 - EES zmenove poziadavky</t>
-        </is>
-      </c>
-      <c r="E34" s="8" t="inlineStr">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>EP-12811</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="C34" s="6" t="inlineStr">
+        <is>
+          <t>Externé požiadavky - delegovanie požiadaviek</t>
+        </is>
+      </c>
+      <c r="D34" s="6" t="inlineStr">
+        <is>
+          <t>EP-12353 – EES zmenové požiadavky</t>
+        </is>
+      </c>
+      <c r="E34" s="5" t="inlineStr">
         <is>
           <t>poseidon-2.10.0</t>
         </is>
       </c>
-      <c r="F34" s="8" t="inlineStr">
+      <c r="F34" s="5" t="inlineStr">
         <is>
           <t>2026-05-05</t>
         </is>
       </c>
-      <c r="G34" s="8" t="inlineStr">
-        <is>
-          <t>DONE</t>
-        </is>
-      </c>
-      <c r="H34" s="9" t="inlineStr"/>
+      <c r="G34" s="5" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="H34" s="6" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="7" t="inlineStr">
-        <is>
-          <t>EP-12807</t>
-        </is>
-      </c>
-      <c r="B35" s="8" t="inlineStr">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>EP-12817</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
         <is>
           <t>Chyba</t>
         </is>
       </c>
-      <c r="C35" s="9" t="inlineStr">
-        <is>
-          <t>Požiadavky CPS - Po kliknuti na tlacidlo Ulozit je pouzivatel odhlaseny zo systemu, ak je stav poziadavky Odoslana na OvZP</t>
-        </is>
-      </c>
-      <c r="D35" s="9" t="inlineStr">
-        <is>
-          <t>EP-12353 - EES zmenove poziadavky</t>
-        </is>
-      </c>
-      <c r="E35" s="8" t="inlineStr">
+      <c r="C35" s="6" t="inlineStr">
+        <is>
+          <t>Požiadavky CPS - Pri filtrovani a kliknuti na Enter sa vytvori nova poziadavka</t>
+        </is>
+      </c>
+      <c r="D35" s="6" t="inlineStr">
+        <is>
+          <t>EP-12353 – EES zmenové požiadavky</t>
+        </is>
+      </c>
+      <c r="E35" s="5" t="inlineStr">
         <is>
           <t>poseidon-2.10.0</t>
         </is>
       </c>
-      <c r="F35" s="8" t="inlineStr">
+      <c r="F35" s="5" t="inlineStr">
         <is>
           <t>2026-05-05</t>
         </is>
       </c>
-      <c r="G35" s="8" t="inlineStr">
-        <is>
-          <t>DONE</t>
-        </is>
-      </c>
-      <c r="H35" s="9" t="inlineStr"/>
+      <c r="G35" s="5" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="H35" s="6" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="7" t="inlineStr">
-        <is>
-          <t>EP-12811</t>
-        </is>
-      </c>
-      <c r="B36" s="8" t="inlineStr">
-        <is>
-          <t>Story</t>
-        </is>
-      </c>
-      <c r="C36" s="9" t="inlineStr">
-        <is>
-          <t>Externé požiadavky - delegovanie požiadaviek</t>
-        </is>
-      </c>
-      <c r="D36" s="9" t="inlineStr">
-        <is>
-          <t>EP-12353 - EES zmenove poziadavky</t>
-        </is>
-      </c>
-      <c r="E36" s="8" t="inlineStr">
+      <c r="A36" s="4" t="inlineStr">
+        <is>
+          <t>EP-12818</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="C36" s="6" t="inlineStr">
+        <is>
+          <t>Externé požiadavky - premenovania stavov + názvy tlačidiel</t>
+        </is>
+      </c>
+      <c r="D36" s="6" t="inlineStr">
+        <is>
+          <t>EP-12353 – EES zmenové požiadavky</t>
+        </is>
+      </c>
+      <c r="E36" s="5" t="inlineStr">
         <is>
           <t>poseidon-2.10.0</t>
         </is>
       </c>
-      <c r="F36" s="8" t="inlineStr">
+      <c r="F36" s="5" t="inlineStr">
         <is>
           <t>2026-05-05</t>
         </is>
       </c>
-      <c r="G36" s="8" t="inlineStr">
-        <is>
-          <t>DONE</t>
-        </is>
-      </c>
-      <c r="H36" s="9" t="inlineStr"/>
+      <c r="G36" s="5" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="H36" s="6" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="7" t="inlineStr">
-        <is>
-          <t>EP-12817</t>
-        </is>
-      </c>
-      <c r="B37" s="8" t="inlineStr">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>EP-12821</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="C37" s="6" t="inlineStr">
+        <is>
+          <t>Externé požiadavky - stornovanie požiadavky</t>
+        </is>
+      </c>
+      <c r="D37" s="6" t="inlineStr">
+        <is>
+          <t>EP-12353 – EES zmenové požiadavky</t>
+        </is>
+      </c>
+      <c r="E37" s="5" t="inlineStr">
+        <is>
+          <t>poseidon-2.10.0</t>
+        </is>
+      </c>
+      <c r="F37" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-05</t>
+        </is>
+      </c>
+      <c r="G37" s="5" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="H37" s="6" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="inlineStr">
+        <is>
+          <t>EP-12846</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="inlineStr">
         <is>
           <t>Chyba</t>
         </is>
       </c>
-      <c r="C37" s="9" t="inlineStr">
-        <is>
-          <t>Požiadavky CPS - Pri filtrovani a kliknuti na Enter sa vytvori nova poziadavka</t>
-        </is>
-      </c>
-      <c r="D37" s="9" t="inlineStr">
-        <is>
-          <t>EP-12353 - EES zmenove poziadavky</t>
-        </is>
-      </c>
-      <c r="E37" s="8" t="inlineStr">
+      <c r="C38" s="6" t="inlineStr">
+        <is>
+          <t>Požiadavky - Používateľ z OvZP nevidí svoju požiadavku v stave nová (rozpracovaná)</t>
+        </is>
+      </c>
+      <c r="D38" s="6" t="inlineStr">
+        <is>
+          <t>EP-12353 – EES zmenové požiadavky</t>
+        </is>
+      </c>
+      <c r="E38" s="5" t="inlineStr">
         <is>
           <t>poseidon-2.10.0</t>
         </is>
       </c>
-      <c r="F37" s="8" t="inlineStr">
+      <c r="F38" s="5" t="inlineStr">
         <is>
           <t>2026-05-05</t>
         </is>
       </c>
-      <c r="G37" s="8" t="inlineStr">
-        <is>
-          <t>DONE</t>
-        </is>
-      </c>
-      <c r="H37" s="9" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="7" t="inlineStr">
-        <is>
-          <t>EP-12846</t>
-        </is>
-      </c>
-      <c r="B38" s="8" t="inlineStr">
+      <c r="G38" s="5" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="H38" s="6" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>EP-12889</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="C39" s="6" t="inlineStr">
+        <is>
+          <t>Oprava právomocí [BUG] + Zobrazenie požiadaviek pre pozorovateľa - úprava zobrazených stavov</t>
+        </is>
+      </c>
+      <c r="D39" s="6" t="inlineStr">
+        <is>
+          <t>EP-12353 – EES zmenové požiadavky</t>
+        </is>
+      </c>
+      <c r="E39" s="5" t="inlineStr">
+        <is>
+          <t>poseidon-2.11.0</t>
+        </is>
+      </c>
+      <c r="F39" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="G39" s="5" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="H39" s="6" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="inlineStr">
+        <is>
+          <t>EP-12890</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="C40" s="6" t="inlineStr">
+        <is>
+          <t>Názov pozície schvaľovania - zvýšenie počtu znakov v zadaní názvu</t>
+        </is>
+      </c>
+      <c r="D40" s="6" t="inlineStr">
+        <is>
+          <t>EP-12353 – EES zmenové požiadavky</t>
+        </is>
+      </c>
+      <c r="E40" s="5" t="inlineStr">
+        <is>
+          <t>poseidon-2.11.0</t>
+        </is>
+      </c>
+      <c r="F40" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="G40" s="5" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="H40" s="6" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>EP-12891</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="C41" s="6" t="inlineStr">
+        <is>
+          <t>Vymazanie prílohy v neodoslanej požiadavke</t>
+        </is>
+      </c>
+      <c r="D41" s="6" t="inlineStr">
+        <is>
+          <t>EP-12353 – EES zmenové požiadavky</t>
+        </is>
+      </c>
+      <c r="E41" s="5" t="inlineStr">
+        <is>
+          <t>poseidon-2.11.0</t>
+        </is>
+      </c>
+      <c r="F41" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="G41" s="5" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="H41" s="6" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>EP-12908</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="C42" s="6" t="inlineStr">
+        <is>
+          <t>Nastavenie organizácie pre požiadavku - úprava pre požiadavky OvZP</t>
+        </is>
+      </c>
+      <c r="D42" s="6" t="inlineStr">
+        <is>
+          <t>EP-12353 – EES zmenové požiadavky</t>
+        </is>
+      </c>
+      <c r="E42" s="5" t="inlineStr">
+        <is>
+          <t>poseidon-2.11.0</t>
+        </is>
+      </c>
+      <c r="F42" s="5" t="inlineStr">
+        <is>
+          <t>2026-05-19</t>
+        </is>
+      </c>
+      <c r="G42" s="5" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="H42" s="6" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>EP-12954</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="inlineStr">
         <is>
           <t>Chyba</t>
         </is>
       </c>
-      <c r="C38" s="9" t="inlineStr">
-        <is>
-          <t>Požiadavky - Používateľ z OvZP nevidí svoju požiadavku v stave nová (rozpracovaná)</t>
-        </is>
-      </c>
-      <c r="D38" s="9" t="inlineStr">
-        <is>
-          <t>EP-12353 - EES zmenove poziadavky</t>
-        </is>
-      </c>
-      <c r="E38" s="8" t="inlineStr">
-        <is>
-          <t>poseidon-2.10.0</t>
-        </is>
-      </c>
-      <c r="F38" s="8" t="inlineStr">
-        <is>
-          <t>2026-05-05</t>
-        </is>
-      </c>
-      <c r="G38" s="8" t="inlineStr">
-        <is>
-          <t>DONE</t>
-        </is>
-      </c>
-      <c r="H38" s="9" t="inlineStr"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="7" t="inlineStr">
-        <is>
-          <t>EP-12889</t>
-        </is>
-      </c>
-      <c r="B39" s="8" t="inlineStr">
-        <is>
-          <t>Story</t>
-        </is>
-      </c>
-      <c r="C39" s="9" t="inlineStr">
-        <is>
-          <t>Oprava právomocí [BUG] + Zobrazenie požiadaviek pre pozorovateľa - úprava zobrazených stavov</t>
-        </is>
-      </c>
-      <c r="D39" s="9" t="inlineStr">
-        <is>
-          <t>EP-12353 - EES zmenove poziadavky</t>
-        </is>
-      </c>
-      <c r="E39" s="8" t="inlineStr">
+      <c r="C43" s="6" t="inlineStr">
+        <is>
+          <t>Aministrátor nevie meniť údaje v nastaveniach systému - externé požiadavy</t>
+        </is>
+      </c>
+      <c r="D43" s="6" t="inlineStr">
+        <is>
+          <t>EP-12353 – EES zmenové požiadavky</t>
+        </is>
+      </c>
+      <c r="E43" s="5" t="inlineStr">
         <is>
           <t>poseidon-2.11.0</t>
         </is>
       </c>
-      <c r="F39" s="8" t="inlineStr">
+      <c r="F43" s="5" t="inlineStr">
         <is>
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="G39" s="8" t="inlineStr">
-        <is>
-          <t>DONE</t>
-        </is>
-      </c>
-      <c r="H39" s="9" t="inlineStr"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="7" t="inlineStr">
-        <is>
-          <t>EP-12890</t>
-        </is>
-      </c>
-      <c r="B40" s="8" t="inlineStr">
-        <is>
-          <t>Story</t>
-        </is>
-      </c>
-      <c r="C40" s="9" t="inlineStr">
-        <is>
-          <t>Názov pozície schvaľovania - zvýšenie počtu znakov v zadaní názvu</t>
-        </is>
-      </c>
-      <c r="D40" s="9" t="inlineStr">
-        <is>
-          <t>EP-12353 - EES zmenove poziadavky</t>
-        </is>
-      </c>
-      <c r="E40" s="8" t="inlineStr">
-        <is>
-          <t>poseidon-2.11.0</t>
-        </is>
-      </c>
-      <c r="F40" s="8" t="inlineStr">
+      <c r="G43" s="5" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="H43" s="6" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>EP-12971</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="inlineStr">
+        <is>
+          <t>Chyba</t>
+        </is>
+      </c>
+      <c r="C44" s="6" t="inlineStr">
+        <is>
+          <t>Externe poziadavky - Pozorovatel ma prava zodpovednej osoby</t>
+        </is>
+      </c>
+      <c r="D44" s="6" t="inlineStr">
+        <is>
+          <t>EP-12353 – EES zmenové požiadavky</t>
+        </is>
+      </c>
+      <c r="E44" s="5" t="inlineStr">
+        <is>
+          <t>poseidon-2.11.1</t>
+        </is>
+      </c>
+      <c r="F44" s="5" t="inlineStr">
         <is>
           <t>2026-05-19</t>
         </is>
       </c>
-      <c r="G40" s="8" t="inlineStr">
-        <is>
-          <t>DONE</t>
-        </is>
-      </c>
-      <c r="H40" s="9" t="inlineStr"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="7" t="inlineStr">
-        <is>
-          <t>EP-12891</t>
-        </is>
-      </c>
-      <c r="B41" s="8" t="inlineStr">
-        <is>
-          <t>Story</t>
-        </is>
-      </c>
-      <c r="C41" s="9" t="inlineStr">
-        <is>
-          <t>Vymazanie prílohy v neodoslanej požiadavke</t>
-        </is>
-      </c>
-      <c r="D41" s="9" t="inlineStr">
-        <is>
-          <t>EP-12353 - EES zmenove poziadavky</t>
-        </is>
-      </c>
-      <c r="E41" s="8" t="inlineStr">
-        <is>
-          <t>poseidon-2.11.0</t>
-        </is>
-      </c>
-      <c r="F41" s="8" t="inlineStr">
-        <is>
-          <t>2026-05-19</t>
-        </is>
-      </c>
-      <c r="G41" s="8" t="inlineStr">
-        <is>
-          <t>DONE</t>
-        </is>
-      </c>
-      <c r="H41" s="9" t="inlineStr"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="7" t="inlineStr">
-        <is>
-          <t>EP-12908</t>
-        </is>
-      </c>
-      <c r="B42" s="8" t="inlineStr">
-        <is>
-          <t>Story</t>
-        </is>
-      </c>
-      <c r="C42" s="9" t="inlineStr">
-        <is>
-          <t>Nastavenie organizácie pre požiadavku - úprava pre požiadavky OvZP</t>
-        </is>
-      </c>
-      <c r="D42" s="9" t="inlineStr">
-        <is>
-          <t>EP-12353 - EES zmenove poziadavky</t>
-        </is>
-      </c>
-      <c r="E42" s="8" t="inlineStr">
-        <is>
-          <t>poseidon-2.11.0</t>
-        </is>
-      </c>
-      <c r="F42" s="8" t="inlineStr">
-        <is>
-          <t>2026-05-19</t>
-        </is>
-      </c>
-      <c r="G42" s="8" t="inlineStr">
-        <is>
-          <t>DONE</t>
-        </is>
-      </c>
-      <c r="H42" s="9" t="inlineStr"/>
-    </row>
-    <row r="43">
-      <c r="A43" s="7" t="inlineStr">
-        <is>
-          <t>EP-12971</t>
-        </is>
-      </c>
-      <c r="B43" s="8" t="inlineStr">
-        <is>
-          <t>Chyba</t>
-        </is>
-      </c>
-      <c r="C43" s="9" t="inlineStr">
-        <is>
-          <t>Externe poziadavky - Pozorovatel ma prava zodpovednej osoby</t>
-        </is>
-      </c>
-      <c r="D43" s="9" t="inlineStr">
-        <is>
-          <t>EP-12353 - EES zmenove poziadavky</t>
-        </is>
-      </c>
-      <c r="E43" s="8" t="inlineStr">
-        <is>
-          <t>poseidon-2.11.1</t>
-        </is>
-      </c>
-      <c r="F43" s="8" t="inlineStr">
-        <is>
-          <t>2026-05-19</t>
-        </is>
-      </c>
-      <c r="G43" s="8" t="inlineStr">
-        <is>
-          <t>DONE</t>
-        </is>
-      </c>
-      <c r="H43" s="9" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" s="7" t="inlineStr">
-        <is>
-          <t>EP-12972</t>
-        </is>
-      </c>
-      <c r="B44" s="8" t="inlineStr">
-        <is>
-          <t>Chyba</t>
-        </is>
-      </c>
-      <c r="C44" s="9" t="inlineStr">
-        <is>
-          <t>Externe poziadavky - Uzivatel nevidi svoje poziadavky, ak ma pravomoc pozorovatela na iny druh</t>
-        </is>
-      </c>
-      <c r="D44" s="9" t="inlineStr">
-        <is>
-          <t>EP-12353 - EES zmenove poziadavky</t>
-        </is>
-      </c>
-      <c r="E44" s="8" t="inlineStr">
-        <is>
-          <t>poseidon-2.11.2</t>
-        </is>
-      </c>
-      <c r="F44" s="8" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
-        </is>
-      </c>
-      <c r="G44" s="8" t="inlineStr">
-        <is>
-          <t>DONE</t>
-        </is>
-      </c>
-      <c r="H44" s="9" t="inlineStr"/>
+      <c r="G44" s="5" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="H44" s="6" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
         <is>
-          <t>EP-12793</t>
+          <t>EP-12972</t>
         </is>
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>Dev Sub-task</t>
+          <t>Chyba</t>
         </is>
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>Požiadavky - Nový atribut - Termín spracovania_nový atribut_DEVELOPMENT</t>
+          <t>Externe poziadavky - Uzivatel nevidi svoje poziadavky, ak ma pravomoc pozorovatela na iny druh</t>
         </is>
       </c>
       <c r="D45" s="6" t="inlineStr">
         <is>
-          <t>EP-12792 - Termin spracovania</t>
+          <t>EP-12353 – EES zmenové požiadavky</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
         <is>
-          <t>poseidon-2.10.0</t>
+          <t>poseidon-2.11.2</t>
         </is>
       </c>
       <c r="F45" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="G45" s="5" t="inlineStr">
@@ -2137,163 +2129,139 @@
           <t>DONE</t>
         </is>
       </c>
-      <c r="H45" s="6" t="inlineStr">
-        <is>
-          <t>prevzate z nadradenej story EP-12792</t>
-        </is>
-      </c>
+      <c r="H45" s="6" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" s="4" t="inlineStr">
-        <is>
-          <t>EP-12794</t>
-        </is>
-      </c>
-      <c r="B46" s="5" t="inlineStr">
-        <is>
-          <t>Test Sub-task</t>
-        </is>
-      </c>
-      <c r="C46" s="6" t="inlineStr">
-        <is>
-          <t>Požiadavky - Nový atribut - Termín spracovania_TESTING</t>
-        </is>
-      </c>
-      <c r="D46" s="6" t="inlineStr">
-        <is>
-          <t>EP-12792 - Termin spracovania</t>
-        </is>
-      </c>
-      <c r="E46" s="5" t="inlineStr">
-        <is>
-          <t>poseidon-2.10.0</t>
-        </is>
-      </c>
-      <c r="F46" s="5" t="inlineStr">
-        <is>
-          <t>2026-05-05</t>
-        </is>
-      </c>
-      <c r="G46" s="5" t="inlineStr">
-        <is>
-          <t>DONE</t>
-        </is>
-      </c>
-      <c r="H46" s="6" t="inlineStr">
-        <is>
-          <t>prevzate z nadradenej story EP-12792</t>
+      <c r="A46" s="7" t="inlineStr">
+        <is>
+          <t>EP-13026</t>
+        </is>
+      </c>
+      <c r="B46" s="8" t="inlineStr">
+        <is>
+          <t>Bug Sub-task</t>
+        </is>
+      </c>
+      <c r="C46" s="9" t="inlineStr">
+        <is>
+          <t>CPPSK-TEST - Externe poziadavky - V prehlade poziadaviek sa zobrazuju nespravne stavy</t>
+        </is>
+      </c>
+      <c r="D46" s="9" t="inlineStr">
+        <is>
+          <t>EP-12538 – Zjednocovanie nasadzovania a verzií (PSK)</t>
+        </is>
+      </c>
+      <c r="E46" s="8" t="inlineStr"/>
+      <c r="F46" s="8" t="inlineStr"/>
+      <c r="G46" s="8" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="H46" s="9" t="inlineStr">
+        <is>
+          <t>bez fix verzie (nadradená story EP-12538 je v testovaní); sub-task ponechaný samostatne – nadradená story nie je ticket modulu</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="4" t="inlineStr">
-        <is>
-          <t>EP-12809</t>
-        </is>
-      </c>
-      <c r="B47" s="5" t="inlineStr">
-        <is>
-          <t>Dev Sub-task</t>
-        </is>
-      </c>
-      <c r="C47" s="6" t="inlineStr">
-        <is>
-          <t>Požiadavky - Nový atribut - Termín spracovania_notifikácia_DEVELOPMENT</t>
-        </is>
-      </c>
-      <c r="D47" s="6" t="inlineStr">
-        <is>
-          <t>EP-12792 - Termin spracovania</t>
-        </is>
-      </c>
-      <c r="E47" s="5" t="inlineStr">
-        <is>
-          <t>poseidon-2.10.0</t>
-        </is>
-      </c>
-      <c r="F47" s="5" t="inlineStr">
-        <is>
-          <t>2026-05-05</t>
-        </is>
-      </c>
-      <c r="G47" s="5" t="inlineStr">
-        <is>
-          <t>DONE</t>
-        </is>
-      </c>
-      <c r="H47" s="6" t="inlineStr">
-        <is>
-          <t>prevzate z nadradenej story EP-12792</t>
+      <c r="A47" s="7" t="inlineStr">
+        <is>
+          <t>EP-13028</t>
+        </is>
+      </c>
+      <c r="B47" s="8" t="inlineStr">
+        <is>
+          <t>Bug Sub-task</t>
+        </is>
+      </c>
+      <c r="C47" s="9" t="inlineStr">
+        <is>
+          <t>CPPSK-TEST/EES-TEST - Požiadavky CPS - Chybný názov atribútu v detaile požiadavky a v štatistikách</t>
+        </is>
+      </c>
+      <c r="D47" s="9" t="inlineStr">
+        <is>
+          <t>EP-12538 – Zjednocovanie nasadzovania a verzií (PSK)</t>
+        </is>
+      </c>
+      <c r="E47" s="8" t="inlineStr"/>
+      <c r="F47" s="8" t="inlineStr"/>
+      <c r="G47" s="8" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="H47" s="9" t="inlineStr">
+        <is>
+          <t>bez fix verzie (nadradená story EP-12538 je v testovaní); sub-task ponechaný samostatne – nadradená story nie je ticket modulu</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="4" t="inlineStr">
-        <is>
-          <t>EP-12848</t>
-        </is>
-      </c>
-      <c r="B48" s="5" t="inlineStr">
+      <c r="A48" s="7" t="inlineStr">
+        <is>
+          <t>EP-13047</t>
+        </is>
+      </c>
+      <c r="B48" s="8" t="inlineStr">
         <is>
           <t>Bug Sub-task</t>
         </is>
       </c>
-      <c r="C48" s="6" t="inlineStr">
-        <is>
-          <t>Požiadavky - Nový atribút - Termín spracovania - prekročený termín - bold zobrazenie</t>
-        </is>
-      </c>
-      <c r="D48" s="6" t="inlineStr">
-        <is>
-          <t>EP-12792 - Termin spracovania</t>
-        </is>
-      </c>
-      <c r="E48" s="5" t="inlineStr">
-        <is>
-          <t>poseidon-2.10.0</t>
-        </is>
-      </c>
-      <c r="F48" s="5" t="inlineStr">
-        <is>
-          <t>2026-05-05</t>
-        </is>
-      </c>
-      <c r="G48" s="5" t="inlineStr">
-        <is>
-          <t>DONE</t>
-        </is>
-      </c>
-      <c r="H48" s="6" t="inlineStr"/>
+      <c r="C48" s="9" t="inlineStr">
+        <is>
+          <t>PSK-TEST - Externe poziadavky - Pre externe poziadavky sa nedotahuje atribut Názov organizácie</t>
+        </is>
+      </c>
+      <c r="D48" s="9" t="inlineStr">
+        <is>
+          <t>EP-12538 – Zjednocovanie nasadzovania a verzií (PSK)</t>
+        </is>
+      </c>
+      <c r="E48" s="8" t="inlineStr"/>
+      <c r="F48" s="8" t="inlineStr"/>
+      <c r="G48" s="8" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="H48" s="9" t="inlineStr">
+        <is>
+          <t>bez fix verzie (nadradená story EP-12538 je v testovaní); sub-task ponechaný samostatne – nadradená story nie je ticket modulu</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
         <is>
-          <t>EP-12852</t>
+          <t>EP-9306</t>
         </is>
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>Bug Sub-task</t>
+          <t>Úloha</t>
         </is>
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>Požiadavky - Nový atribut - Termín spracovania - odoslanie notifikácie</t>
+          <t>TTSK - požiadavky CPS - uprava notifikácie</t>
         </is>
       </c>
       <c r="D49" s="6" t="inlineStr">
         <is>
-          <t>EP-12792 - Termin spracovania</t>
+          <t>Samostatné</t>
         </is>
       </c>
       <c r="E49" s="5" t="inlineStr">
         <is>
-          <t>poseidon-2.10.0</t>
+          <t>ttsk-2.4.1</t>
         </is>
       </c>
       <c r="F49" s="5" t="inlineStr">
         <is>
-          <t>2026-05-05</t>
+          <t>2025-03-13</t>
         </is>
       </c>
       <c r="G49" s="5" t="inlineStr">
@@ -2304,330 +2272,98 @@
       <c r="H49" s="6" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="A50" s="7" t="inlineStr">
-        <is>
-          <t>EP-12819</t>
-        </is>
-      </c>
-      <c r="B50" s="8" t="inlineStr">
-        <is>
-          <t>Dev Sub-task</t>
-        </is>
-      </c>
-      <c r="C50" s="9" t="inlineStr">
-        <is>
-          <t>Externé požiadavky - premenovania stavov + názvy tlačidiel_DEVELOPMENT</t>
-        </is>
-      </c>
-      <c r="D50" s="9" t="inlineStr">
-        <is>
-          <t>EP-12818 - premenovania stavov</t>
-        </is>
-      </c>
-      <c r="E50" s="8" t="inlineStr">
-        <is>
-          <t>poseidon-2.10.0</t>
-        </is>
-      </c>
-      <c r="F50" s="8" t="inlineStr">
-        <is>
-          <t>2026-05-05</t>
-        </is>
-      </c>
-      <c r="G50" s="8" t="inlineStr">
-        <is>
-          <t>DONE</t>
-        </is>
-      </c>
-      <c r="H50" s="9" t="inlineStr">
-        <is>
-          <t>prevzate z nadradenej story EP-12818</t>
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>EP-10963</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="inlineStr">
+        <is>
+          <t>Story</t>
+        </is>
+      </c>
+      <c r="C50" s="6" t="inlineStr">
+        <is>
+          <t>Nasadenie funcionality - štatistiky externe požiadavky na trnavavuc-test a psk-test</t>
+        </is>
+      </c>
+      <c r="D50" s="6" t="inlineStr">
+        <is>
+          <t>Samostatné</t>
+        </is>
+      </c>
+      <c r="E50" s="5" t="inlineStr">
+        <is>
+          <t>psk-2.9.0</t>
+        </is>
+      </c>
+      <c r="F50" s="5" t="inlineStr">
+        <is>
+          <t>neuvolnena</t>
+        </is>
+      </c>
+      <c r="G50" s="5" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="H50" s="6" t="inlineStr">
+        <is>
+          <t>verzia zatiaľ nie je označená ako released</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="7" t="inlineStr">
-        <is>
-          <t>EP-12847</t>
-        </is>
-      </c>
-      <c r="B51" s="8" t="inlineStr">
-        <is>
-          <t>Bug Sub-task</t>
-        </is>
-      </c>
-      <c r="C51" s="9" t="inlineStr">
-        <is>
-          <t>Externé požiadavky - premenovanie stavov - štatistiky</t>
-        </is>
-      </c>
-      <c r="D51" s="9" t="inlineStr">
-        <is>
-          <t>EP-12818 - premenovania stavov</t>
-        </is>
-      </c>
-      <c r="E51" s="8" t="inlineStr">
-        <is>
-          <t>poseidon-2.10.0</t>
-        </is>
-      </c>
-      <c r="F51" s="8" t="inlineStr">
-        <is>
-          <t>2026-05-05</t>
-        </is>
-      </c>
-      <c r="G51" s="8" t="inlineStr">
-        <is>
-          <t>DONE</t>
-        </is>
-      </c>
-      <c r="H51" s="9" t="inlineStr">
-        <is>
-          <t>prevzate z nadradenej story EP-12818</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="4" t="inlineStr">
-        <is>
-          <t>EP-12822</t>
-        </is>
-      </c>
-      <c r="B52" s="5" t="inlineStr">
-        <is>
-          <t>Dev Sub-task</t>
-        </is>
-      </c>
-      <c r="C52" s="6" t="inlineStr">
-        <is>
-          <t>Externé požiadavky - stornovanie požiadavky_DEVELOPMENT</t>
-        </is>
-      </c>
-      <c r="D52" s="6" t="inlineStr">
-        <is>
-          <t>EP-12821 - stornovanie poziadavky</t>
-        </is>
-      </c>
-      <c r="E52" s="5" t="inlineStr">
-        <is>
-          <t>poseidon-2.10.0</t>
-        </is>
-      </c>
-      <c r="F52" s="5" t="inlineStr">
-        <is>
-          <t>2026-05-05</t>
-        </is>
-      </c>
-      <c r="G52" s="5" t="inlineStr">
-        <is>
-          <t>DONE</t>
-        </is>
-      </c>
-      <c r="H52" s="6" t="inlineStr">
-        <is>
-          <t>prevzate z nadradenej story EP-12821</t>
-        </is>
-      </c>
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>EP-11775</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="inlineStr">
+        <is>
+          <t>Podpora</t>
+        </is>
+      </c>
+      <c r="C51" s="6" t="inlineStr">
+        <is>
+          <t>[PODPORA] - PODPORA - PSK - nejde vykonať ZFK</t>
+        </is>
+      </c>
+      <c r="D51" s="6" t="inlineStr">
+        <is>
+          <t>Samostatné</t>
+        </is>
+      </c>
+      <c r="E51" s="5" t="inlineStr">
+        <is>
+          <t>psk-2.7.0</t>
+        </is>
+      </c>
+      <c r="F51" s="5" t="inlineStr">
+        <is>
+          <t>2025-12-18</t>
+        </is>
+      </c>
+      <c r="G51" s="5" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="H51" s="6" t="inlineStr"/>
     </row>
     <row r="53">
-      <c r="A53" s="7" t="inlineStr">
-        <is>
-          <t>EP-13026</t>
-        </is>
-      </c>
-      <c r="B53" s="8" t="inlineStr">
-        <is>
-          <t>Bug Sub-task</t>
-        </is>
-      </c>
-      <c r="C53" s="9" t="inlineStr">
-        <is>
-          <t>CPPSK-TEST - Externe poziadavky - V prehlade poziadaviek sa zobrazuju nespravne stavy</t>
-        </is>
-      </c>
-      <c r="D53" s="9" t="inlineStr">
-        <is>
-          <t>EP-12538 - Zjednocovanie nasadzovania (PSK)</t>
-        </is>
-      </c>
-      <c r="E53" s="8" t="inlineStr"/>
-      <c r="F53" s="8" t="inlineStr"/>
-      <c r="G53" s="8" t="inlineStr">
-        <is>
-          <t>DONE</t>
-        </is>
-      </c>
-      <c r="H53" s="9" t="inlineStr">
-        <is>
-          <t>nadradena story EP-12538 nema fix verziu (v testovani)</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="7" t="inlineStr">
-        <is>
-          <t>EP-13047</t>
-        </is>
-      </c>
-      <c r="B54" s="8" t="inlineStr">
-        <is>
-          <t>Bug Sub-task</t>
-        </is>
-      </c>
-      <c r="C54" s="9" t="inlineStr">
-        <is>
-          <t>PSK-TEST - Externe poziadavky - Pre externe poziadavky sa nedotahuje atribut Názov organizácie</t>
-        </is>
-      </c>
-      <c r="D54" s="9" t="inlineStr">
-        <is>
-          <t>EP-12538 - Zjednocovanie nasadzovania (PSK)</t>
-        </is>
-      </c>
-      <c r="E54" s="8" t="inlineStr"/>
-      <c r="F54" s="8" t="inlineStr"/>
-      <c r="G54" s="8" t="inlineStr">
-        <is>
-          <t>DONE</t>
-        </is>
-      </c>
-      <c r="H54" s="9" t="inlineStr">
-        <is>
-          <t>nadradena story EP-12538 nema fix verziu (v testovani)</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="4" t="inlineStr">
-        <is>
-          <t>EP-9306</t>
-        </is>
-      </c>
-      <c r="B55" s="5" t="inlineStr">
-        <is>
-          <t>Úloha</t>
-        </is>
-      </c>
-      <c r="C55" s="6" t="inlineStr">
-        <is>
-          <t>TTSK - požiadavky CPS - uprava notifikácie</t>
-        </is>
-      </c>
-      <c r="D55" s="6" t="inlineStr">
-        <is>
-          <t>Samostatne</t>
-        </is>
-      </c>
-      <c r="E55" s="5" t="inlineStr">
-        <is>
-          <t>ttsk-2.4.1</t>
-        </is>
-      </c>
-      <c r="F55" s="5" t="inlineStr">
-        <is>
-          <t>2025-03-13</t>
-        </is>
-      </c>
-      <c r="G55" s="5" t="inlineStr">
-        <is>
-          <t>DONE</t>
-        </is>
-      </c>
-      <c r="H55" s="6" t="inlineStr"/>
-    </row>
-    <row r="56">
-      <c r="A56" s="4" t="inlineStr">
-        <is>
-          <t>EP-10964</t>
-        </is>
-      </c>
-      <c r="B56" s="5" t="inlineStr">
-        <is>
-          <t>Dev Sub-task</t>
-        </is>
-      </c>
-      <c r="C56" s="6" t="inlineStr">
-        <is>
-          <t>Nasadenie funcionality - štatistiky externe požiadavky na trnavavuc-test a psk-test_DEVELOPMENT</t>
-        </is>
-      </c>
-      <c r="D56" s="6" t="inlineStr">
-        <is>
-          <t>Samostatne</t>
-        </is>
-      </c>
-      <c r="E56" s="5" t="inlineStr">
-        <is>
-          <t>psk-2.9.0</t>
-        </is>
-      </c>
-      <c r="F56" s="5" t="inlineStr">
-        <is>
-          <t>neuvolnena</t>
-        </is>
-      </c>
-      <c r="G56" s="5" t="inlineStr">
-        <is>
-          <t>DONE</t>
-        </is>
-      </c>
-      <c r="H56" s="6" t="inlineStr">
-        <is>
-          <t>prevzate z nadradenej story EP-10963; verzia este nie je uvolnena</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="4" t="inlineStr">
-        <is>
-          <t>EP-11775</t>
-        </is>
-      </c>
-      <c r="B57" s="5" t="inlineStr">
-        <is>
-          <t>Podpora</t>
-        </is>
-      </c>
-      <c r="C57" s="6" t="inlineStr">
-        <is>
-          <t>[PODPORA] - PODPORA - PSK - nejde vykonať ZFK</t>
-        </is>
-      </c>
-      <c r="D57" s="6" t="inlineStr">
-        <is>
-          <t>Samostatne</t>
-        </is>
-      </c>
-      <c r="E57" s="5" t="inlineStr">
-        <is>
-          <t>psk-2.7.0</t>
-        </is>
-      </c>
-      <c r="F57" s="5" t="inlineStr">
-        <is>
-          <t>2025-12-18</t>
-        </is>
-      </c>
-      <c r="G57" s="5" t="inlineStr">
-        <is>
-          <t>DONE</t>
-        </is>
-      </c>
-      <c r="H57" s="6" t="inlineStr"/>
-    </row>
-    <row r="59">
-      <c r="B59" s="10" t="inlineStr">
+      <c r="B53" s="10" t="inlineStr">
         <is>
           <t>Spolu ticketov:</t>
         </is>
       </c>
-      <c r="C59" s="10">
-        <f>COUNTA(A5:A57)</f>
+      <c r="C53" s="10">
+        <f>COUNTA(A5:A51)</f>
         <v/>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:H57"/>
+  <autoFilter ref="A4:H51"/>
   <mergeCells count="2">
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A1:H1"/>
@@ -2680,12 +2416,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A49" r:id="rId45"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A50" r:id="rId46"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A51" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A52" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A53" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A54" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A55" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A56" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A57" r:id="rId53"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
